--- a/Översikt TANUM.xlsx
+++ b/Översikt TANUM.xlsx
@@ -601,7 +601,7 @@
         <v>44488</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45217</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45530</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45156</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>45637</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>46029</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>46145</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45400</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45008</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>46034</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44692</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45135</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44644</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45160</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45197</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>46247</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>45761</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45833</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>44621</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>46141</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45317</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45534</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>45274</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44613</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44462</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>44511</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>44725</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>44725</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45196</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45769</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>44879</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>45246</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>45362</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>45722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>45649</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44719</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>45889</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45982</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>46161</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>45236</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>46070</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45247</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>46103</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45685</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45791</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>45866</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44481</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44506</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44552</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44544</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44601</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>44573</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44573</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>44470</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>44596</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>44573</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44501</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44862</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>44722</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44470</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44459</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44837</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>44563</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>44506</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>44506</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>44506</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>44573</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>44731</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>44802</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>44802</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>44791</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44525</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44470</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>44463</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44802</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44830</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44593</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>44484</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44817</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44506</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44470</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44487</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>45273</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44890</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44999</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45488</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44490</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45649</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44954</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45208</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45159</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45261</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45005</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45265</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45355</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45102</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>45686</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44997</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44606</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>45293</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>44526</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>44544</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>44496</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>45085</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>45579</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>45506</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>45506</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>45209</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>45210</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44514</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>45384</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>44887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>45659</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>45168</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>45425</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>45425</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>45637</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>44799</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>45568</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>44792</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>44739</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>45744</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>45515</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>45145</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>45300</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>45162</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44862</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>45446</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>45645</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>45645</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>44872</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45516</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>45002</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44627</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45239</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44552</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44867</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45211</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>45355</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>45677</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>45187</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45252</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44579</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44939</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45041</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45747</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45271</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45155</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>45350</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>45629</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45107</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>45154</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45552</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45596</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45490</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>45369</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>44839</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>46139</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>45293</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>44506</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45170</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>45889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>45887</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
         <v>45889</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>45889</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>45673</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>45390</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>45895</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>45895</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45387</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45597</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>45895</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>45168</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45895</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>45635</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>45903</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>45902</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44585</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45903</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>45698</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>44908</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45334</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45104</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>45987</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>45755</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>45824</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>45838</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45837</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>45872</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44469</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45286</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>45196</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>45922</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45923</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45922</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45820</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>46029</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>45925</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45929</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>45927</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>45926</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>45929</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>45926</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45321</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>45932</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>45935</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>45174</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>45937</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>44522</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45184</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45942</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45943</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>45026</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>45945</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45946</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45946</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45951</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45951</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45949</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>45951</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45951</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44946</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45952</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>44572</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45954</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45954</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45958</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45538</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>45196</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>45739</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45273</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>44846</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>45971</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>45972</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45972</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>45454</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45311</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45974</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>45698</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45978</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>44867</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>44900</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>45985</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>44807</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45987</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44944</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45756</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45303</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45303</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>45595</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>45673</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>44467</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45469</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45265</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>45268</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>44538</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45469</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45566</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45036</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45281</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45303</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45303</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45599</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>46162</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45085</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>46000</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>46000</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>46000</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>45190</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>45946</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>46013</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>46013</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45673</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45237</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>44929</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45015</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45655</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>44585</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45236</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45761</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>46029</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>46029</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>46207</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44719</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>46031</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>45387</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>46034</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>46037</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>44830</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>46038</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>46039</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44725</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>46038</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>46038</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>46042</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>44725</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>46129</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46044</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>46044</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>46044</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>46044</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>45603</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>46044</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>46044</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>44544</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>46044</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>46044</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>46044</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>46175</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>46176</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>44969</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>46176</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>46178</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45273</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>46058</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>46177</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45374</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45525</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45030</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>46178</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>45355</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>45102</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45023</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>46071</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>45085</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>46071</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>44573</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45279</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>46183</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44858</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>45026</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>46084</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>46084</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>46083</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>45239</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>46085</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>44799</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45597</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>45267</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45400</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45267</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>46190</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>45371</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>45722</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>46093</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44872</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45075</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>46100</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>44832</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>46099</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>45260</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>46100</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45384</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>45272</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>44601</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45575</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44591</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>45309</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>46125</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>46199</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45029</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>46010</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>45259</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29858,7 +29858,7 @@
         <v>45278</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>45628</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>45659</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44817</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>45271</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>46204</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>44890</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>44651</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>45035</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         <v>46247</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>45596</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>45463</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>46206</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>46206</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45450</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44841</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45538</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45231</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>45392</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>46251</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>45155</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45063</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>46209</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>46254</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45544</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>44908</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45440</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>44698</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>45154</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>46259</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>46258</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>44964</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44573</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>44879</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32350,7 +32350,7 @@
         <v>45170</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>45692</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>44613</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44897</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>46258</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>46260</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>45209</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>46262</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>45168</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>45153</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>45371</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45168</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45571</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>46267</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>44834</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>44488</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45754</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>45754</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>45415</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45748</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>46231</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>46231</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>46273</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34029,7 +34029,7 @@
         <v>46272</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>46272</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>46272</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>46273</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>45072</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         <v>46276</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>46276</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>45789</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>45726</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>45791</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>45737</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45737</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45743</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45362</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45551</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>46273</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>44879</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45301</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45084</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45743</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45728</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>45392</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35640,7 +35640,7 @@
         <v>46241</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35713,7 +35713,7 @@
         <v>46240</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>45805</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>45593</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45324</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36005,7 +36005,7 @@
         <v>45753</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36078,7 +36078,7 @@
         <v>45819</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>45834</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>45834</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>45842</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36370,7 +36370,7 @@
         <v>45820</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45842</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>45842</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>45842</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>45522</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45872</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>45874</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>45873</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>45874</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>45874</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45709</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45880</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45880</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45880</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>45722</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>45362</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>44586</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>44636</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44509</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>45204</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>46133</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>

--- a/Översikt TANUM.xlsx
+++ b/Översikt TANUM.xlsx
@@ -601,7 +601,7 @@
         <v>44488</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45217</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45530</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45156</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>46029</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>46247</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45000</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>46145</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45400</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>46034</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45135</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>45000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44644</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45197</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45160</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45761</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45833</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>44621</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>46141</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45534</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>44613</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>45274</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>46272</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44511</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44725</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44725</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45236</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44719</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>45889</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44879</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>46070</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>46103</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45649</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45982</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45685</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>46161</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45246</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45247</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>45362</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>45769</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45387</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45722</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45791</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44481</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44506</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44544</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44552</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44573</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44573</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44470</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44596</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44601</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44573</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44501</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44862</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44722</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44470</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44837</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44735</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44563</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44506</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44506</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44506</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44573</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44802</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>44802</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44731</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44470</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>44802</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>44830</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>44593</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>44484</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44817</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44506</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44470</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>44487</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>45281</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>45187</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45272</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>44725</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>44490</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45400</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>44862</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>45236</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>45374</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>45390</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>45239</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45208</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45252</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>45698</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44872</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>44872</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44839</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>45209</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45210</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>44879</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45450</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45595</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>44830</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45387</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>45268</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>44890</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>45231</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>45084</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>45490</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>46013</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44573</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>46013</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45301</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45265</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>45551</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45392</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44879</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>46029</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45743</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45362</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>45728</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45538</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>46031</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>46034</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>45722</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>45425</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45425</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>44858</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>45155</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>45887</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>45889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>45889</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>46038</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>46038</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>46038</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>46037</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44601</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>45895</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>45303</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>46042</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45895</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>46039</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>45895</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>45895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>46044</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>46044</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>46044</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>46044</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>46044</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>46044</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>46044</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>46044</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>46044</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>45902</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>44488</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>45903</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45903</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45538</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45029</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>46058</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>45506</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45506</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>44939</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>45922</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45922</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45568</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45923</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>45023</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>45925</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45571</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>46071</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>46071</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45926</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>45805</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45926</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45929</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45927</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>45929</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>46083</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45753</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45593</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>45932</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45575</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>46084</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>46084</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>46085</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45267</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45579</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>45935</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>45629</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>44719</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45937</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>46093</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44867</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45324</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45942</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>46099</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>46100</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45946</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45945</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>46100</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>45949</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>45597</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45596</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45946</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>45951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>45951</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>45168</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>45952</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>45951</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45951</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45954</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45279</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45271</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45954</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45041</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45958</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>44946</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>46125</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>46010</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45971</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44969</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45972</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>44954</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45974</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45972</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45637</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45978</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45102</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>44929</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>44997</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45659</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45985</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45673</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45987</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45673</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45005</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45159</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>44469</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45755</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>46000</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>46000</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45026</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45872</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>45168</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>46000</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>45085</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>45820</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45824</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44832</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>44506</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>45686</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>46139</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45819</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>44807</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>45987</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45677</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45739</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45369</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45838</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45837</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>44908</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>46029</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>45744</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>44585</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>45597</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>44467</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45063</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>44846</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45834</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45834</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44887</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45259</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45168</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45842</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>46162</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45842</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45842</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>45293</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>45469</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45820</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>45645</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45645</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45946</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>46207</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45211</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44817</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45469</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46129</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45522</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>45488</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45145</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>44544</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>44964</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>44999</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>46175</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>46177</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>45384</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45384</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>46176</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45392</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>46176</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>46178</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45552</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>46178</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>44579</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45698</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45566</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44544</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44572</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45874</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45260</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>46183</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45872</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45873</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>44522</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>45463</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45874</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44613</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45170</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>45371</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>45874</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>44591</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>44514</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>46190</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45355</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45525</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>45761</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>44526</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>45446</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>45709</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>45596</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>45168</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45035</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45196</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>45880</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>46199</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45880</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>45880</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>44627</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>44552</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>45321</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>44606</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45673</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>44698</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>46204</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45107</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>46209</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>46206</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45085</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28713,7 +28713,7 @@
         <v>46206</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>46251</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45655</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>46254</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>46258</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>45190</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45085</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>46259</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45440</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>46260</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>46258</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>45649</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>45154</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>46262</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>45754</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44651</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45756</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44792</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45303</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>45303</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>45154</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44799</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>44739</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>45293</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>46267</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44725</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>45300</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>44799</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>46272</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45271</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>46272</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>46272</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31049,7 +31049,7 @@
         <v>46231</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>46273</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>46231</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>46273</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>45015</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>45309</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>45030</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>46276</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45273</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45267</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>46276</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>44496</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>45278</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>45104</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45628</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45265</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45355</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44834</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45303</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>44897</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>46273</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>44585</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>46240</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>44908</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>44573</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>46241</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45261</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45184</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>46286</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>46286</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>46286</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45155</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>46287</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>44867</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45371</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45350</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>44538</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>46247</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45002</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45286</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45544</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45036</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45722</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45387</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44944</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45153</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45311</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>45599</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>45692</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45162</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45516</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45415</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>44890</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44900</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45754</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45102</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45209</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45355</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45659</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45635</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>45239</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45174</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>45075</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>45170</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45196</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45273</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45334</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>45026</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>45728</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45273</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36164,7 +36164,7 @@
         <v>45237</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45747</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45454</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45515</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>45603</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>44841</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45748</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>45072</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45789</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45791</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>45743</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45737</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45737</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>45726</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44586</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>44636</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45362</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44509</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45204</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>46133</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>

--- a/Översikt TANUM.xlsx
+++ b/Översikt TANUM.xlsx
@@ -601,7 +601,7 @@
         <v>44488</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45217</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45530</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45156</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>46029</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>46247</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45000</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>46145</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45400</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>46034</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45135</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>45000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44644</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45197</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45160</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45761</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45833</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>44621</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>46141</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45534</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>44613</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>45274</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>46272</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44511</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44725</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44725</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45236</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44719</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>45889</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44879</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>46070</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>46103</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45649</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45982</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45685</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>46161</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45246</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45247</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>45362</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>45769</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45387</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45722</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45791</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44481</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44506</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44544</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44552</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44573</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44573</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44470</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44596</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44601</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44573</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44501</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44862</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44722</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44470</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44837</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44735</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44563</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44506</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44506</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44506</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44573</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44802</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>44802</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44731</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44470</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>44802</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>44830</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>44593</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>44484</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44817</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44506</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44470</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>44487</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>45281</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>45187</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45272</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>44725</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>44490</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45400</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>44862</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>45236</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>45374</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>45390</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>45239</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45208</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45252</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>45698</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44872</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>44872</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44839</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>45209</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45210</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>44879</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45450</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45595</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>44830</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45387</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>45268</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>44890</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>45231</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>45084</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>45490</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>46013</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44573</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>46013</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45301</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45265</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>45551</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45392</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44879</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>46029</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45743</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45362</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>45728</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45538</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>46031</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>46034</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>45722</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>45425</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45425</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>44858</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>45155</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>45887</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>45889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>45889</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>46038</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>46038</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>46038</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>46037</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44601</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>45895</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>45303</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>46042</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45895</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>46039</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>45895</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>45895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>46044</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>46044</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>46044</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>46044</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>46044</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>46044</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>46044</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>46044</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>46044</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>45902</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>44488</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>45903</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45903</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45538</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45029</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>46058</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>45506</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45506</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>44939</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>45922</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45922</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45568</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45923</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>45023</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>45925</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45571</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>46071</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>46071</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45926</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>45805</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45926</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45929</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45927</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>45929</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>46083</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45753</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45593</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>45932</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45575</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>46084</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>46084</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>46085</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45267</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45579</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>45935</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>45629</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>44719</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45937</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>46093</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44867</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45324</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45942</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>46099</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>46100</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45946</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45945</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>46100</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>45949</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>45597</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45596</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45946</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>45951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>45951</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>45168</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>45952</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>45951</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45951</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45954</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45279</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45271</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45954</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45041</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45958</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>44946</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>46125</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>46010</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45971</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44969</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45972</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>44954</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45974</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45972</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45637</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45978</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45102</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>44929</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>44997</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45659</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45985</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45673</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45987</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45673</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45005</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45159</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>44469</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45755</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>46000</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>46000</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45026</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45872</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>45168</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>46000</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>45085</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>45820</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45824</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44832</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>44506</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>45686</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>46139</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45819</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>44807</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>45987</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45677</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45739</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45369</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45838</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45837</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>44908</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>46029</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>45744</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>44585</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>45597</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>44467</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45063</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>44846</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45834</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45834</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44887</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45259</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45168</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45842</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>46162</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45842</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45842</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>45293</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>45469</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45820</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>45645</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45645</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45946</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>46207</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45211</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44817</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45469</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46129</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45522</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>45488</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45145</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>44544</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>44964</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>44999</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>46175</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>46177</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>45384</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45384</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>46176</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45392</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>46176</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>46178</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45552</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>46178</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>44579</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45698</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45566</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44544</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44572</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45874</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45260</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>46183</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45872</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45873</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>44522</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>45463</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45874</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44613</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45170</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>45371</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>45874</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>44591</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>44514</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>46190</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45355</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45525</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>45761</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>44526</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>45446</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>45709</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>45596</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>45168</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45035</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45196</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>45880</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>46199</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45880</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>45880</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>44627</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>44552</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>45321</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>44606</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45673</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>44698</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>46204</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45107</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>46209</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>46206</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45085</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28713,7 +28713,7 @@
         <v>46206</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>46251</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45655</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>46254</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>46258</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>45190</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45085</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>46259</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45440</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>46260</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>46258</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>45649</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>45154</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>46262</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>45754</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44651</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45756</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44792</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45303</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>45303</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>45154</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44799</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>44739</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>45293</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>46267</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44725</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>45300</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>44799</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>46272</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45271</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>46272</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>46272</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31049,7 +31049,7 @@
         <v>46231</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>46273</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>46231</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>46273</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>45015</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>45309</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>45030</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>46276</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45273</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45267</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>46276</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>44496</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>45278</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>45104</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45628</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45265</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45355</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44834</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45303</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>44897</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>46273</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>44585</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>46240</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>44908</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>44573</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>46241</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45261</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45184</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>46286</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>46286</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>46286</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45155</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>46287</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>44867</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45371</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45350</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>44538</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>46247</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45002</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45286</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45544</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45036</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45722</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45387</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44944</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45153</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45311</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>45599</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>45692</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45162</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45516</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45415</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>44890</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44900</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45754</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45102</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45209</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45355</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45659</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45635</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>45239</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45174</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>45075</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>45170</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45196</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45273</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45334</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>45026</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>45728</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45273</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36164,7 +36164,7 @@
         <v>45237</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45747</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45454</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45515</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>45603</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>44841</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45748</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>45072</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45789</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45791</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>45743</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45737</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45737</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>45726</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44586</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>44636</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45362</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44509</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45204</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>46133</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>

--- a/Översikt TANUM.xlsx
+++ b/Översikt TANUM.xlsx
@@ -601,7 +601,7 @@
         <v>44488</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45217</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45530</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45156</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>46029</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>46247</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45000</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>46145</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45400</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>46034</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>44692</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45135</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>45000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>45722</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44644</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45160</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45197</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45761</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45833</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>44621</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45317</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>46141</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45534</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>45274</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46272</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44613</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44511</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44725</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44725</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45196</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>45791</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>45889</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>46070</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>44879</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>46103</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45362</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45982</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>45722</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>45649</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45866</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>46161</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>44719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>45236</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45247</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45685</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44481</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44506</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44544</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44552</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44601</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44573</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44573</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44596</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44573</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44501</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44862</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44722</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44837</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44735</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44563</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44506</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44506</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44506</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44573</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44791</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44802</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44731</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44525</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>44802</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44802</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44830</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>44484</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>44817</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>44506</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>44487</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>45273</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45488</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44890</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>45293</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>45649</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>44490</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44954</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>44999</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>45208</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45159</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45261</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>45005</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>45265</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>44544</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>45102</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45355</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45686</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44997</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44606</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45789</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44526</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>45726</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45579</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45791</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44496</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45737</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>45085</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>46013</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>46013</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>45737</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>45506</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>45506</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>45209</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>45210</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44514</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>45889</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45384</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45889</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>45895</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45895</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>46029</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44887</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>46029</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45743</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45895</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45895</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45637</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>44799</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>46031</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45568</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45659</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>46034</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45168</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>45425</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>45425</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>45903</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>45902</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>45903</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>46037</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>46038</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>46039</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>46038</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>46038</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>44792</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>46042</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>45362</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>45551</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>45744</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>46044</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>46044</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>46044</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44879</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>46044</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>45301</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>45084</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>46044</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>46044</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>45743</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>46044</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45728</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>45392</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>46044</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>46044</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44739</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45145</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>45515</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45922</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>45805</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45923</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45300</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45162</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45922</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44872</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45925</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>45929</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45927</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>46058</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45926</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>45929</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45926</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44862</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45446</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>45645</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45516</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45002</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44627</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45932</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45239</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45935</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>46071</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44552</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45937</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>46071</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44867</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45593</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>45942</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>45211</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>45355</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>45187</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>45945</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>45677</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>45946</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45946</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>45324</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>45753</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45951</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45951</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45949</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45252</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45951</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>46084</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>46084</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45952</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>46083</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>46085</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45954</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45954</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45958</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44579</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45267</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>44939</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45041</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45747</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>46093</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45971</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>45271</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45350</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45155</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45629</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>46100</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>46099</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45972</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45972</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>46100</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>45974</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45107</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45154</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45978</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45552</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45819</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45596</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45985</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>45987</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>46125</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45490</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>44839</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>46010</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45085</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45293</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>46000</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>46000</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>46000</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45170</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45673</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45834</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45390</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45834</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45387</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45597</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45168</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45635</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45820</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45842</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44585</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45698</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45334</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45842</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45842</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45104</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>45369</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>46139</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44506</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45286</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45196</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45522</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>45728</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45321</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44908</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45987</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45755</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>45824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>45174</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45838</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>45837</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>44522</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45872</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45184</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45026</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45820</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>45872</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46029</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>44946</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>44572</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45874</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45538</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45196</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45739</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45273</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44846</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>45873</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45874</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45874</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45454</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45469</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45311</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>45698</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>46162</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>44867</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>45709</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44900</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45946</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44807</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45880</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>44944</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45756</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45880</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45303</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>45303</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45595</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>45673</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>46207</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>45880</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45469</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45722</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>46129</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>46175</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45265</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>45268</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44538</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>46176</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>46176</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>46178</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>45887</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27243,7 +27243,7 @@
         <v>46177</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>46178</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>45566</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>45036</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>45281</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>46183</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>45303</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>45303</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>45599</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>46190</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>45371</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>45190</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>45673</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>45237</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>44929</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45015</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45655</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44585</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>45236</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>45761</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>46199</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44719</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>46204</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>45387</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>46206</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>46206</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>44830</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44725</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>46209</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>44725</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>45603</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>44544</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>46259</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>46258</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>44969</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>46258</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>46260</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>45273</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>46262</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>45374</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45525</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>46267</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>45030</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45355</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45102</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45023</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45085</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44573</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45279</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>46231</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>46231</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>46273</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>44858</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>46272</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>46272</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45026</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>46272</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>46273</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>46276</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45239</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>46276</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>44799</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>45597</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>45267</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45400</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>45722</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>44872</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45075</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44832</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>46240</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45260</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45384</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>46241</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>46273</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>46286</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45272</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44601</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45575</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>46286</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>46286</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>44591</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>45309</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45029</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>46292</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>46251</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>46293</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45259</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>46247</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>45278</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>45628</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>46287</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>45659</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44817</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>45271</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44890</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44651</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>45035</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>46294</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>45596</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45463</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45450</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>46254</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>44841</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45538</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>45231</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>45392</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>45155</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45063</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45544</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>44908</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45440</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44698</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>45154</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>44964</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44573</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>44879</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45170</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45692</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>44613</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44897</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>45209</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45168</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36164,7 +36164,7 @@
         <v>45153</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45371</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45168</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45571</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>44834</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>44488</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45754</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>45754</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45415</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45748</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>45072</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45362</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>44586</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>44636</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44509</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45204</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>46133</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>

--- a/Översikt TANUM.xlsx
+++ b/Översikt TANUM.xlsx
@@ -601,7 +601,7 @@
         <v>44488</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45217</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45530</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45156</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>46029</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>46247</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45000</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>46145</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45400</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>46034</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>44692</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45135</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>45000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>45722</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44644</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45160</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45197</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45761</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45833</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>44621</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45317</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>46141</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45534</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>45274</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46272</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44613</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44511</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44725</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44725</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45196</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>45791</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>45889</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>46070</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>44879</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>46103</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45362</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45982</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>45722</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>45649</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45866</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>46161</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>44719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>45236</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45247</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45685</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44481</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44506</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44544</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44552</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44601</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44573</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44573</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44596</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44573</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44501</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44862</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44722</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44837</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44735</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44563</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44506</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44506</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44506</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44573</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44791</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44802</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44731</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44525</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>44802</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44802</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44830</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>44484</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>44817</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>44506</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>44487</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>45273</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45488</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44890</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>45293</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>45649</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>44490</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44954</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>44999</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>45208</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45159</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45261</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>45005</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>45265</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>44544</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>45102</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45355</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45686</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44997</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44606</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45789</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44526</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>45726</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45579</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45791</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44496</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45737</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>45085</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>46013</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>46013</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>45737</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>45506</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>45506</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>45209</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>45210</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44514</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>45889</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45384</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45889</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>45895</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45895</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>46029</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44887</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>46029</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45743</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45895</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45895</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45637</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>44799</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>46031</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45568</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45659</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>46034</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45168</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>45425</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>45425</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>45903</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>45902</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>45903</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>46037</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>46038</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>46039</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>46038</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>46038</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>44792</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>46042</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>45362</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>45551</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>45744</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>46044</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>46044</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>46044</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44879</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>46044</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>45301</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>45084</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>46044</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>46044</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>45743</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>46044</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45728</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>45392</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>46044</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>46044</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44739</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45145</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>45515</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45922</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>45805</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45923</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45300</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45162</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45922</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44872</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45925</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>45929</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45927</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>46058</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45926</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>45929</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45926</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44862</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45446</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>45645</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45516</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45002</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44627</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45932</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45239</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45935</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>46071</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44552</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45937</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>46071</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44867</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45593</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>45942</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>45211</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>45355</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>45187</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>45945</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>45677</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>45946</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45946</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>45324</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>45753</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45951</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45951</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45949</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45252</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45951</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>46084</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>46084</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45952</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>46083</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>46085</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45954</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45954</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45958</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44579</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45267</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>44939</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45041</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45747</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>46093</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45971</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>45271</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45350</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45155</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45629</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>46100</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>46099</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45972</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45972</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>46100</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>45974</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45107</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45154</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45978</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45552</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45819</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45596</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45985</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>45987</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>46125</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45490</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>44839</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>46010</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45085</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45293</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>46000</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>46000</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>46000</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45170</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45673</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45834</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45390</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45834</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45387</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45597</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45168</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45635</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45820</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45842</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44585</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45698</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45334</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45842</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45842</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45104</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>45369</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>46139</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44506</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45286</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45196</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45522</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>45728</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45321</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44908</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45987</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45755</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>45824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>45174</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45838</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>45837</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>44522</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45872</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45184</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45026</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45820</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>45872</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46029</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>44946</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>44572</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45874</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45538</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45196</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45739</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45273</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44846</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>45873</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45874</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45874</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45454</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45469</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45311</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>45698</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>46162</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>44867</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>45709</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44900</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45946</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44807</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45880</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>44944</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45756</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45880</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45303</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>45303</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45595</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>45673</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>46207</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>45880</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45469</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45722</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>46129</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>46175</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45265</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>45268</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44538</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>46176</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>46176</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>46178</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>45887</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27243,7 +27243,7 @@
         <v>46177</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>46178</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>45566</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>45036</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>45281</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>46183</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>45303</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>45303</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>45599</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>46190</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>45371</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>45190</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>45673</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>45237</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>44929</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45015</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45655</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44585</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>45236</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>45761</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>46199</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44719</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>46204</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>45387</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>46206</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>46206</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>44830</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44725</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>46209</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>44725</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>45603</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>44544</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>46259</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>46258</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>44969</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>46258</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>46260</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>45273</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>46262</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>45374</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45525</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>46267</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>45030</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45355</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45102</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45023</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45085</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44573</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45279</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>46231</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>46231</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>46273</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>44858</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>46272</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>46272</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45026</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>46272</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>46273</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>46276</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45239</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>46276</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>44799</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>45597</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>45267</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45400</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>45722</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>44872</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45075</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44832</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>46240</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45260</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45384</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>46241</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>46273</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>46286</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45272</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44601</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45575</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>46286</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>46286</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>44591</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>45309</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45029</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>46292</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>46251</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>46293</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45259</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>46247</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>45278</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>45628</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>46287</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>45659</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44817</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>45271</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44890</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44651</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>45035</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>46294</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>45596</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45463</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45450</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>46254</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>44841</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45538</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>45231</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>45392</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>45155</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45063</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45544</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>44908</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45440</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44698</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>45154</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>44964</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44573</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>44879</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45170</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45692</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>44613</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44897</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>45209</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45168</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36164,7 +36164,7 @@
         <v>45153</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45371</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45168</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45571</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>44834</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>44488</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45754</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>45754</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45415</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45748</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>45072</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45362</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>44586</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>44636</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44509</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45204</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>46133</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>

--- a/Översikt TANUM.xlsx
+++ b/Översikt TANUM.xlsx
@@ -601,7 +601,7 @@
         <v>44488</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45217</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45156</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>45637</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>46029</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>46247</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45000</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>45400</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>46145</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45008</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>46034</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45135</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44692</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>45000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>45722</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44644</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45761</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45197</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45160</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45833</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>44621</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>44613</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>45274</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45317</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>46141</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>45534</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44511</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44725</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44725</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45236</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>45387</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>45722</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44719</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45889</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>44879</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45649</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>45246</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45247</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>45362</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45769</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45866</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45685</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45982</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>46103</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>46070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>46161</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44481</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44506</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44544</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44552</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44573</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44573</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44601</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44596</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44573</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44501</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44862</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44722</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44837</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44735</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44506</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44563</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44506</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44506</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44506</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44573</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44802</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44830</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>44487</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44791</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44731</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44802</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>44802</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>44525</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>44593</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>45374</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44484</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45063</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45390</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44846</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45698</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45208</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>45239</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45252</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45692</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>44839</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>44872</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>44872</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45209</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>45210</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>45516</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>44879</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45281</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45415</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44887</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>44890</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45187</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>45272</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44900</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>45259</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>45168</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>44725</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>45450</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45595</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>45754</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>44830</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>44490</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>45400</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>45102</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>45293</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>45268</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>45645</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>45645</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44862</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>45236</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45387</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45209</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>45355</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>45659</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>45231</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>45635</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45239</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>45490</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44890</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45174</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45075</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>44573</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45170</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>45196</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45211</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>45722</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45265</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>44817</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45469</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45273</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45488</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45145</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44544</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45887</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>44964</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45334</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45538</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44999</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45889</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>45026</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45895</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45895</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45895</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45895</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>45425</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45425</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44858</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45155</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45902</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45728</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45273</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45237</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45747</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45903</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45903</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45454</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45515</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>44601</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45603</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45384</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45384</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45303</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45392</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>44841</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45552</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44579</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>44488</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45748</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45698</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>45566</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44544</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>44572</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45538</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45072</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45260</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45029</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>45506</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45506</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44522</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45463</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>45922</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>44613</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45170</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>44939</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45789</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>44591</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45922</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44514</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45568</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45923</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45355</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>45925</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>45926</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45525</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>45761</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45023</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45791</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>45571</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>44526</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>45446</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>45926</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45743</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>45737</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45596</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>45168</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45929</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45927</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>45737</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>45035</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>45726</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>45084</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>45196</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>45301</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45929</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45551</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45392</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44879</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45743</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45362</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45728</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>44627</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>44552</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45575</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45932</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>45579</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>45629</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>44719</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20132,7 +20132,7 @@
         <v>45935</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>45321</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>44606</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>45673</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
         <v>44698</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>44867</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>45107</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>45805</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>45085</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>45597</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45937</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45596</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45753</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>45593</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45168</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45324</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>45942</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>45655</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>45946</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>45945</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>45279</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45271</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45041</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45949</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45946</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45819</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>45190</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44946</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45951</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45951</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45085</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45440</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45952</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>44969</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45951</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>45951</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45954</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45954</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>45958</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>45834</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45834</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44954</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45637</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>45649</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>45102</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>44929</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>45154</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>44997</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>45754</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45659</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44651</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>45842</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45756</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45842</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45971</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45673</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45842</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45673</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>44792</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>45303</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45303</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45820</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>45154</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45972</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45005</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45159</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>45974</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45972</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44799</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>44739</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45978</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>45293</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>44725</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>45522</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45300</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>44799</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>45026</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>45168</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>45271</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>45874</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>44832</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>45872</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45873</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>45874</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>45686</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>45874</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45015</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45709</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>45309</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44807</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>45030</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>45880</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45677</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>45880</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45880</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45273</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>45267</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>44496</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45739</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45278</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>46099</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45104</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>46100</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>46100</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>45628</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>45985</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45265</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>45355</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>44834</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>45987</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>45303</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>45744</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>44897</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44585</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45597</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>44585</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>44908</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44573</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>46125</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>46010</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>45261</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>46000</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>46000</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>45184</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>46000</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>45085</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45155</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44867</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>45371</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45350</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44538</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45002</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45286</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>45544</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>46013</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>46013</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>45755</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45036</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>46029</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>45722</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>46029</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45872</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>46031</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45820</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>46034</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45824</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45387</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>44944</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44506</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>46038</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>46038</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>46038</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>46037</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>46042</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>46139</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>46039</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45153</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45987</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>46044</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>46044</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>46044</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>46044</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>46044</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>46044</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>46044</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>46044</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>46044</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>45369</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45311</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45599</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45838</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>45837</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>44908</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>46058</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>46029</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>46071</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>46071</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>46083</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>46084</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>46084</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>46085</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45267</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>46093</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>46162</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45469</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45946</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>46207</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>46129</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>46175</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>46177</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>46176</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>46176</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>46178</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>46178</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>46183</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45371</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>46190</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>46199</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>46204</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>46209</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>46206</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>46206</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>46267</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>46272</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>46272</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>46272</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>46231</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>46273</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>46231</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>46273</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>46276</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>46276</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>46273</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>46240</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>46241</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>46286</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>46286</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>46286</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>46247</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36164,7 +36164,7 @@
         <v>46287</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>46251</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>46292</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>46293</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>46294</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>46254</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>46258</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>46300</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>46259</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>46258</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>46262</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>46260</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>44586</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>44636</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45362</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>44509</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45204</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>46133</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>

--- a/Översikt TANUM.xlsx
+++ b/Översikt TANUM.xlsx
@@ -601,7 +601,7 @@
         <v>44488</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45217</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45156</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>45637</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>46029</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>46247</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45000</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>45400</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>46145</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45008</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>46034</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45135</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44692</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>45000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>45722</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44644</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45761</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45197</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45160</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45833</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>44621</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>44613</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>45274</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45317</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>46141</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>45534</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44511</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44725</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44725</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45236</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>45387</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>45722</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44719</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45889</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>44879</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45649</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>45246</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45247</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>45362</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45769</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45866</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45685</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45982</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>46103</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>46070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>46161</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44481</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44506</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44544</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44552</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44573</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44573</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44601</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44596</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44573</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44501</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44862</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44722</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44837</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44735</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44506</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44563</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44506</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44506</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44506</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44573</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44802</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44830</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>44487</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44791</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44731</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44802</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>44802</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>44525</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>44593</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>45374</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44484</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45063</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45390</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44846</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45698</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45208</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>45239</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45252</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45692</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>44839</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>44872</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>44872</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45209</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>45210</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>45516</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>44879</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45281</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45415</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44887</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>44890</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45187</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>45272</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44900</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>45259</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>45168</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>44725</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>45450</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45595</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>45754</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>44830</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>44490</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>45400</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>45102</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>45293</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>45268</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>45645</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>45645</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44862</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>45236</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45387</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45209</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>45355</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>45659</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>45231</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>45635</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45239</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>45490</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44890</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45174</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45075</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>44573</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45170</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>45196</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45211</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>45722</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45265</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>44817</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45469</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45273</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45488</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45145</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44544</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45887</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>44964</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45334</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45538</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44999</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45889</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>45026</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45895</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45895</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45895</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45895</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>45425</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45425</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44858</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45155</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45902</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45728</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45273</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45237</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45747</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45903</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45903</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45454</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45515</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>44601</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45603</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45384</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45384</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45303</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45392</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>44841</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45552</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44579</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>44488</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45748</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45698</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>45566</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44544</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>44572</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45538</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45072</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45260</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45029</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>45506</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45506</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44522</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45463</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>45922</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>44613</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45170</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>44939</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45789</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>44591</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45922</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44514</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45568</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45923</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45355</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>45925</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>45926</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45525</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>45761</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45023</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45791</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>45571</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>44526</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>45446</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>45926</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45743</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>45737</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45596</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>45168</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45929</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45927</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>45737</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>45035</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>45726</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>45084</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>45196</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>45301</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45929</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45551</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45392</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44879</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45743</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45362</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45728</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>44627</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>44552</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45575</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45932</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>45579</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>45629</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>44719</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20132,7 +20132,7 @@
         <v>45935</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>45321</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>44606</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>45673</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
         <v>44698</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>44867</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>45107</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>45805</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>45085</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>45597</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45937</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45596</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45753</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>45593</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45168</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45324</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>45942</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>45655</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>45946</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>45945</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>45279</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45271</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45041</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45949</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45946</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45819</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>45190</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44946</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45951</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45951</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45085</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45440</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45952</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>44969</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45951</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>45951</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45954</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45954</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>45958</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>45834</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45834</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44954</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45637</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>45649</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>45102</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>44929</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>45154</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>44997</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>45754</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45659</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44651</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>45842</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45756</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45842</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45971</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45673</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45842</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45673</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>44792</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>45303</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45303</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45820</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>45154</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45972</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45005</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45159</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>45974</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45972</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44799</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>44739</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45978</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>45293</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>44725</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>45522</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45300</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>44799</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>45026</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>45168</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>45271</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>45874</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>44832</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>45872</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45873</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>45874</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>45686</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>45874</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45015</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45709</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>45309</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44807</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>45030</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>45880</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45677</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>45880</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45880</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45273</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>45267</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>44496</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45739</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45278</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>46099</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45104</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>46100</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>46100</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>45628</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>45985</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45265</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>45355</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>44834</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>45987</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>45303</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>45744</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>44897</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44585</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45597</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>44585</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>44908</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44573</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>46125</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>46010</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>45261</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>46000</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>46000</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>45184</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>46000</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>45085</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45155</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44867</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>45371</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45350</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44538</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45002</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45286</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>45544</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>46013</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>46013</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>45755</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45036</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>46029</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>45722</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>46029</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45872</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>46031</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45820</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>46034</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45824</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45387</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>44944</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44506</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>46038</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>46038</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>46038</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>46037</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>46042</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>46139</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>46039</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45153</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45987</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>46044</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>46044</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>46044</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>46044</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>46044</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>46044</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>46044</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>46044</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>46044</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>45369</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45311</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45599</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45838</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>45837</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>44908</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>46058</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>46029</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>46071</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>46071</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>46083</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>46084</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>46084</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>46085</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45267</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>46093</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>46162</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45469</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45946</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>46207</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>46129</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>46175</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>46177</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>46176</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>46176</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>46178</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>46178</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>46183</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45371</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>46190</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>46199</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>46204</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>46209</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>46206</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>46206</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>46267</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>46272</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>46272</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>46272</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>46231</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>46273</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>46231</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>46273</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>46276</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>46276</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>46273</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>46240</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>46241</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>46286</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>46286</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>46286</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>46247</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36164,7 +36164,7 @@
         <v>46287</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>46251</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>46292</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>46293</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>46294</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>46254</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>46258</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>46300</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>46259</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>46258</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>46262</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>46260</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>44586</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>44636</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45362</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>44509</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45204</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>46133</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>

--- a/Översikt TANUM.xlsx
+++ b/Översikt TANUM.xlsx
@@ -601,7 +601,7 @@
         <v>44488</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>45530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45156</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45799</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>46029</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>46247</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>46145</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45400</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>45008</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>46034</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>44692</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45135</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>45000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44644</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>45160</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45197</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>45833</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44621</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>46141</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45317</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>45534</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45274</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>46272</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>44613</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44511</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44725</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45769</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>44879</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>45246</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45362</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45722</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44719</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>45889</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>46161</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45982</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>45236</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>46070</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>46103</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45247</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>45685</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45791</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>46308</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45866</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>44506</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>44552</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>44544</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44601</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44573</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44573</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44596</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44573</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44501</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>44862</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44722</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44837</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44563</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44506</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44506</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44506</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44573</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44791</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44802</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44731</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>44802</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44525</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44802</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44817</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44506</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44487</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>45273</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>44890</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45293</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44999</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45488</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>44490</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45649</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>45208</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44954</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>45159</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>45261</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45005</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>45265</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>45355</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45102</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>45686</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>44997</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44544</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45579</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44606</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44496</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>45506</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>45506</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45085</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>45209</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>45210</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>44514</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>45384</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>44887</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45659</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>44799</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45568</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45168</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45425</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>45425</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         <v>44792</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>44739</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45744</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>45145</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>44526</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>45515</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>45300</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45162</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>44862</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>45446</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>45645</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>45645</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>45516</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>44872</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>44552</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>45239</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>45211</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>45355</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44867</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>45187</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>45677</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>45252</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>45002</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>44579</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44939</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>45041</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45747</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45271</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45155</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45629</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45350</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44627</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45107</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45154</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>45596</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45552</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45369</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>46139</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>44506</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45887</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45889</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45490</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45889</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>44839</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>45293</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45895</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45895</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>45170</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45895</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45895</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44908</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>45987</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>45755</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45824</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45838</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>45837</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45673</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>45872</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45903</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>45902</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>45390</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>45903</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>45820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>46029</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>45387</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>45597</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45168</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>45635</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>44585</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>45698</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45334</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45922</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45923</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45104</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>45922</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45925</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>45929</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>45927</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>45926</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45929</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45926</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>45932</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>45286</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>45196</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>45935</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>45937</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>45728</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45942</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>45945</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45321</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45946</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>45946</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         <v>45951</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>45951</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>45949</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45951</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>45951</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>45952</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45174</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45954</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45954</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45958</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>44522</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>45184</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45026</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45971</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>45469</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>44946</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45972</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45972</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>44572</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45974</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>45978</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>46162</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>45538</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>45196</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45985</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>45739</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45987</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>45273</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>44846</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45946</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>45454</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45311</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>45698</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>45085</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20163,7 +20163,7 @@
         <v>46000</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>44867</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>46000</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>46000</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44900</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>46207</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44807</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>44944</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>45756</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>45303</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>45303</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>45595</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>45673</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45469</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>46013</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>46013</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45265</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45268</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>46129</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>44538</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>45566</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>45036</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>46029</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>46029</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45281</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>45303</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45303</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>45599</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>46175</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>46031</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>46034</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>46176</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>46176</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>46178</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>46037</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>46038</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>46038</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>46038</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>46177</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>46178</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>46044</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>46044</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>46044</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>46044</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>46044</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>46044</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>46044</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>46044</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>46044</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45190</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>46183</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45673</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>46058</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45237</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>44929</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45015</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45655</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44585</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45236</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>46071</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45761</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>46071</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44719</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45387</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>46084</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>46084</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>46083</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>46085</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>46190</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>44830</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>44725</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45371</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45267</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44725</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45603</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>46093</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>44544</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>46100</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>46099</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>46100</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>44969</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>45273</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45374</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>45525</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45030</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>45355</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>45102</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>45023</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45085</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>46125</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>46199</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>44573</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>46010</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>45279</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>44858</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>45026</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>46204</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>45239</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>44799</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>46206</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>46206</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>45597</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45267</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>45400</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45722</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>44872</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45075</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>44832</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>45260</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>46209</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45384</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45272</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44601</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45575</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>44591</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>46231</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>46231</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>45309</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>46273</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>46272</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>46272</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>46272</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>46273</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45029</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45259</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29391,7 +29391,7 @@
         <v>45278</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>45628</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>46276</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45659</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>44817</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>46276</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>45271</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>44890</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>44651</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>45035</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45596</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45463</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45450</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>46240</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>44841</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>46241</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45538</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>45231</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45392</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>46273</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>46286</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>46286</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>46286</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45155</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45063</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45544</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44908</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45440</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>44698</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45154</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>44964</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>46292</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31737,7 +31737,7 @@
         <v>44573</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>44879</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45170</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>45692</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>46251</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>44613</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>46293</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>44897</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>46247</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>46287</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45209</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45168</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45153</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45371</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45168</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>46294</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45571</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44834</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>44488</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>46254</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45754</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>46258</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45754</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45415</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>45748</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>46258</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45072</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>46300</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46260</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45789</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>45726</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45791</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45737</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>46259</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>45737</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>45743</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45362</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>45551</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>44879</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45301</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45084</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>45743</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45728</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>45392</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>46262</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45805</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>46307</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>46039</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45593</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45842</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45324</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45753</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45819</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>46267</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45834</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45834</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45820</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45842</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45842</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>45522</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45872</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45874</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45873</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45874</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45874</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>45709</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45880</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>45880</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>45880</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45722</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>45362</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>44586</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>44636</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44509</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>45204</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>46133</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>

--- a/Översikt TANUM.xlsx
+++ b/Översikt TANUM.xlsx
@@ -601,7 +601,7 @@
         <v>44488</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>45530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45156</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45799</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>46029</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>46247</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>46145</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45400</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>45008</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>46034</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>44692</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45135</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>45000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44644</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>45160</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45197</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>45833</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44621</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>46141</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45317</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>45534</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45274</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>46272</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>44613</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44511</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44725</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45769</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>44879</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>45246</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45362</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45722</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44719</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>45889</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>46161</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45982</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>45236</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>46070</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>46103</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45247</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>45685</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45791</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>46308</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45866</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>44506</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>44552</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>44544</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44601</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44573</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44573</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44596</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44573</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44501</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>44862</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44722</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44837</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44563</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44506</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44506</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44506</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44573</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44791</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44802</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44731</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>44802</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44525</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44802</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44817</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44506</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44487</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>45273</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>44890</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45293</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44999</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45488</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>44490</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45649</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>45208</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44954</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>45159</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>45261</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45005</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>45265</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>45355</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45102</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>45686</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>44997</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44544</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45579</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44606</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44496</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>45506</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>45506</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45085</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>45209</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>45210</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>44514</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>45384</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>44887</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45659</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>44799</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45568</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45168</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45425</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>45425</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         <v>44792</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>44739</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45744</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>45145</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>44526</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>45515</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>45300</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45162</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>44862</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>45446</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>45645</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>45645</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>45516</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>44872</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>44552</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>45239</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>45211</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>45355</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44867</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>45187</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>45677</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>45252</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>45002</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>44579</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44939</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>45041</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45747</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45271</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45155</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45629</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45350</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44627</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45107</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45154</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>45596</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45552</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45369</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>46139</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>44506</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45887</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45889</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45490</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45889</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>44839</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>45293</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45895</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45895</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>45170</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45895</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45895</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44908</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>45987</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>45755</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45824</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45838</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>45837</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45673</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>45872</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45903</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>45902</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>45390</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>45903</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>45820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>46029</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>45387</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>45597</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45168</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>45635</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>44585</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>45698</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45334</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45922</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45923</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45104</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>45922</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45925</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>45929</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>45927</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>45926</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45929</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45926</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>45932</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>45286</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>45196</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>45935</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>45937</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>45728</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45942</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>45945</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45321</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45946</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>45946</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         <v>45951</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>45951</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>45949</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45951</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>45951</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>45952</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45174</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45954</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45954</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45958</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>44522</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>45184</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45026</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45971</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>45469</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>44946</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45972</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45972</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>44572</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45974</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>45978</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>46162</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>45538</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>45196</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45985</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>45739</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45987</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>45273</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>44846</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45946</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>45454</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45311</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>45698</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>45085</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20163,7 +20163,7 @@
         <v>46000</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>44867</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>46000</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>46000</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44900</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>46207</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44807</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>44944</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>45756</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>45303</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>45303</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>45595</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>45673</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45469</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>46013</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>46013</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45265</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45268</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>46129</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>44538</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>45566</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>45036</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>46029</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>46029</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45281</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>45303</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45303</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>45599</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>46175</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>46031</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>46034</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>46176</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>46176</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>46178</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>46037</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>46038</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>46038</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>46038</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>46177</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>46178</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>46044</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>46044</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>46044</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>46044</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>46044</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>46044</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>46044</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>46044</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>46044</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45190</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>46183</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45673</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>46058</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45237</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>44929</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45015</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45655</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44585</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45236</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>46071</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45761</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>46071</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44719</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45387</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>46084</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>46084</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>46083</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>46085</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>46190</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>44830</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>44725</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45371</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45267</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44725</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45603</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>46093</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>44544</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>46100</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>46099</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>46100</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>44969</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>45273</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45374</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>45525</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45030</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>45355</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>45102</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>45023</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45085</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>46125</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>46199</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>44573</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>46010</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>45279</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>44858</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>45026</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>46204</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>45239</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>44799</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>46206</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>46206</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>45597</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45267</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>45400</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45722</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>44872</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45075</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>44832</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>45260</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>46209</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45384</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45272</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44601</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45575</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>44591</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>46231</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>46231</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>45309</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>46273</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>46272</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>46272</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>46272</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>46273</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45029</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45259</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29391,7 +29391,7 @@
         <v>45278</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>45628</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>46276</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45659</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>44817</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>46276</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>45271</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>44890</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>44651</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>45035</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45596</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45463</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45450</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>46240</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>44841</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>46241</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45538</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>45231</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45392</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>46273</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>46286</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>46286</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>46286</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45155</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45063</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45544</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44908</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45440</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>44698</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45154</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>44964</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>46292</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31737,7 +31737,7 @@
         <v>44573</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>44879</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45170</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>45692</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>46251</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>44613</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>46293</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>44897</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>46247</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>46287</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45209</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45168</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45153</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45371</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45168</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>46294</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45571</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44834</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>44488</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>46254</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45754</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>46258</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45754</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45415</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>45748</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>46258</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45072</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>46300</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46260</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45789</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>45726</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45791</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45737</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>46259</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>45737</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>45743</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45362</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>45551</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>44879</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45301</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45084</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>45743</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45728</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>45392</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>46262</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45805</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>46307</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>46039</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45593</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45842</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45324</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45753</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45819</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>46267</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45834</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45834</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45820</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45842</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45842</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>45522</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45872</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45874</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45873</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45874</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45874</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>45709</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45880</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>45880</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>45880</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45722</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>45362</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>44586</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>44636</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44509</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>45204</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>46133</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>

--- a/Översikt TANUM.xlsx
+++ b/Översikt TANUM.xlsx
@@ -601,7 +601,7 @@
         <v>44488</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>45217</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45156</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45799</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>46029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>46247</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>46145</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45400</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>46034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45008</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45135</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45000</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>44692</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44644</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>45197</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>45160</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>45833</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44621</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45534</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>46272</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>46141</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44613</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45274</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45317</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44511</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44725</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44719</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45889</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45236</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46161</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45387</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45722</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>45982</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45791</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>46070</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>46103</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>45866</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>44879</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>46308</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45649</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45685</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>45196</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>45246</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>45247</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>45362</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45769</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>44506</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>44544</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>44552</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44601</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44573</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44573</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44596</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44573</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44501</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>44862</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44722</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44837</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44563</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44506</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44506</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44506</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44573</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44791</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44802</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44731</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>44802</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44525</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44802</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44817</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44506</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45722</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45281</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44867</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45187</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>45889</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45272</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>45371</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45895</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>44725</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>45895</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45895</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>45895</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>45350</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45400</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>44538</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45002</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45286</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45544</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44862</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>45236</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>45374</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>45902</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45903</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>45903</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>45390</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>45036</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>45722</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>46162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45387</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>45698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45922</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>44944</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45922</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45153</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45946</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>45923</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>45925</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>45926</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>45926</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>45929</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45927</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45208</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>46129</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45239</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>45929</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>45932</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>45935</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45252</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44839</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44872</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>44872</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>45311</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>45599</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45937</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>46175</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45209</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>44879</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45942</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>46177</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>46176</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45450</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45595</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>44830</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>46176</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45946</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45945</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45692</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>45162</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>46178</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45949</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>45516</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45951</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45951</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45415</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45952</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45951</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45951</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>45954</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>44890</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44900</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>46183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45954</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>45958</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45754</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45268</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>45102</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>45371</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>46190</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45387</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>45209</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>45355</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45971</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45659</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>45635</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>45972</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45239</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45974</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>45972</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>45174</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>46199</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45075</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45978</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>45170</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>45196</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45273</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45231</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45334</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>46204</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>45985</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>46209</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>46206</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45490</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45026</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>45987</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>46206</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>45728</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>45273</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>45237</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>44890</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45747</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>45454</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44573</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45515</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>45603</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>46000</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>44841</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>46000</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>46000</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45748</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45085</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45072</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>46231</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>46231</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>46013</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>46013</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>45789</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>46029</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45791</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>46029</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>46031</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>46034</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>45265</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>45743</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>45737</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>45737</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45726</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>45084</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>46240</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45301</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>46038</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>46038</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>45551</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>46038</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45392</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>46241</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>46037</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44879</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45743</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>46042</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45362</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45728</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>46286</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>46044</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>46044</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>46044</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>46044</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>46044</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>46044</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>46286</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>46286</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>46044</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>46044</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>46044</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45805</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>46247</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45753</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>46058</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>45593</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>45324</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>46287</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>46251</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>46292</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>46293</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>46294</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>46071</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>46071</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45819</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>46083</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>46084</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>46084</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45834</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45834</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>46085</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45538</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45267</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>46254</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>46258</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>46093</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45842</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>46300</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45842</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>46099</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46100</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>46100</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45820</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45425</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45425</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>44858</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45155</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>46259</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>45522</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>46258</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>45874</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>46260</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>46125</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45872</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45873</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>45874</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>46010</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45874</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44601</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45709</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45880</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>46262</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45303</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>45880</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>45880</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45538</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45842</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>45029</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>46267</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>45506</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45506</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>46039</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>46307</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45755</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44939</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45872</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>46314</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45820</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45568</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45824</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>45023</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45571</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44506</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>46316</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>46139</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>46272</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>46178</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45987</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>46273</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>46272</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>46273</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>46272</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>46273</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>46207</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45369</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45575</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45838</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45837</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45579</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>46276</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>46276</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>44908</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>45629</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44719</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>46029</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44867</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>45597</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45596</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>45168</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>45279</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45271</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>45041</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>44946</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>44969</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44954</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45637</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>45102</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>44929</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44997</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45659</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45673</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45673</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45005</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>45159</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>45026</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45168</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44832</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45686</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>44807</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45677</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45739</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45744</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44585</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45597</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45063</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44846</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>44887</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>45259</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45168</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>45293</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>45645</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>45645</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>45211</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44817</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45469</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45488</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>45145</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>44544</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44964</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>44999</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>45384</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45384</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45392</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>45552</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31737,7 +31737,7 @@
         <v>44579</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>45698</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45566</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44544</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44572</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>45260</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>44522</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45463</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44613</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45170</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44591</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44514</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45355</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45525</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45761</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44526</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45446</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45596</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>45168</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45035</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>45196</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44627</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>44552</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>45321</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44606</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>45673</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44698</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45107</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45085</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>45655</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45190</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45085</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45440</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>45649</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45154</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45754</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>44651</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>45756</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>44792</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45303</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45303</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>45154</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>44799</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44739</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45293</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44725</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45300</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>44799</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45271</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45015</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45309</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45030</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45273</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45267</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44496</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45278</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45104</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45628</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45265</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45355</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>44834</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>45303</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>44897</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>44585</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44908</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44573</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45261</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45184</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45155</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>44586</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>44636</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45362</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44509</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>45204</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>46133</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>

--- a/Översikt TANUM.xlsx
+++ b/Översikt TANUM.xlsx
@@ -601,7 +601,7 @@
         <v>44488</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>45217</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45156</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45799</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>46029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>46247</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>46145</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45400</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>46034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45008</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45135</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45000</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>44692</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44644</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>45197</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>45160</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>45833</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44621</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45534</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>46272</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>46141</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44613</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45274</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45317</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44511</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44725</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44719</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45889</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45236</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46161</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45387</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45722</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>45982</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45791</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>46070</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>46103</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>45866</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>44879</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>46308</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45649</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45685</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>45196</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>45246</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>45247</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>45362</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45769</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>44506</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>44544</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>44552</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44601</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44573</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44573</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44596</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44573</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44501</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>44862</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44722</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44837</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44563</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44506</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44506</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44506</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44573</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44791</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44802</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44731</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>44802</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44525</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44802</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44817</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44506</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45722</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45281</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44867</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45187</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>45889</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45272</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>45371</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45895</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>44725</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>45895</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45895</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>45895</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>45350</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45400</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>44538</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45002</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45286</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45544</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44862</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>45236</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>45374</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>45902</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45903</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>45903</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>45390</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>45036</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>45722</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>46162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45387</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>45698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45922</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>44944</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45922</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45153</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45946</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>45923</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>45925</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>45926</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>45926</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>45929</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45927</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45208</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>46129</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45239</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>45929</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>45932</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>45935</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45252</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44839</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44872</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>44872</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>45311</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>45599</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45937</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>46175</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45209</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>44879</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45942</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>46177</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>46176</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45450</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45595</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>44830</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>46176</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45946</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45945</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45692</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>45162</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>46178</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45949</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>45516</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45951</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45951</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45415</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45952</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45951</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45951</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>45954</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>44890</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44900</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>46183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45954</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>45958</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45754</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45268</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>45102</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>45371</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>46190</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45387</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>45209</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>45355</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45971</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45659</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>45635</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>45972</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45239</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45974</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>45972</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>45174</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>46199</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45075</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45978</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>45170</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>45196</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45273</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45231</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45334</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>46204</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>45985</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>46209</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>46206</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45490</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45026</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>45987</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>46206</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>45728</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>45273</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>45237</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>44890</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45747</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>45454</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44573</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45515</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>45603</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>46000</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>44841</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>46000</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>46000</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45748</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45085</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45072</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>46231</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>46231</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>46013</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>46013</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>45789</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>46029</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45791</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>46029</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>46031</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>46034</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>45265</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>45743</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>45737</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>45737</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45726</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>45084</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>46240</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45301</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>46038</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>46038</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>45551</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>46038</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45392</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>46241</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>46037</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44879</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45743</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>46042</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45362</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45728</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>46286</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>46044</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>46044</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>46044</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>46044</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>46044</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>46044</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>46286</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>46286</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>46044</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>46044</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>46044</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45805</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>46247</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45753</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>46058</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>45593</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>45324</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>46287</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>46251</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>46292</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>46293</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>46294</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>46071</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>46071</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45819</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>46083</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>46084</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>46084</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45834</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45834</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>46085</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45538</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45267</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>46254</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>46258</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>46093</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45842</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>46300</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45842</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>46099</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46100</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>46100</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45820</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45425</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45425</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>44858</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45155</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>46259</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>45522</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>46258</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>45874</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>46260</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>46125</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45872</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45873</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>45874</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>46010</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45874</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44601</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45709</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45880</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>46262</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45303</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>45880</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>45880</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45538</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45842</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>45029</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>46267</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>45506</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45506</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>46039</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>46307</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45755</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44939</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45872</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>46314</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45820</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45568</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45824</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>45023</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45571</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44506</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>46316</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>46139</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>46272</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>46178</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45987</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>46273</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>46272</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>46273</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>46272</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>46273</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>46207</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45369</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45575</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45838</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45837</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45579</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>46276</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>46276</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>44908</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>45629</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44719</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>46029</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44867</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>45597</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45596</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>45168</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>45279</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45271</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>45041</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>44946</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>44969</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44954</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45637</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>45102</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>44929</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44997</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45659</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45673</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45673</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45005</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>45159</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>45026</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45168</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44832</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45686</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>44807</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45677</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45739</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45744</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44585</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45597</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45063</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44846</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>44887</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>45259</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45168</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>45293</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>45645</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>45645</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>45211</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44817</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45469</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45488</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>45145</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>44544</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44964</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>44999</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>45384</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45384</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45392</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>45552</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31737,7 +31737,7 @@
         <v>44579</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>45698</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45566</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44544</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44572</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>45260</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>44522</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45463</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44613</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45170</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44591</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44514</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45355</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45525</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45761</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44526</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45446</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45596</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>45168</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45035</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>45196</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44627</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>44552</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>45321</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44606</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>45673</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44698</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45107</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45085</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>45655</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45190</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45085</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45440</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>45649</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45154</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45754</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>44651</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>45756</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>44792</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45303</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45303</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>45154</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>44799</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44739</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45293</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44725</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45300</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>44799</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45271</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45015</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45309</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45030</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45273</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45267</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44496</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45278</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45104</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45628</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45265</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45355</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>44834</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>45303</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>44897</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>44585</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44908</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44573</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45261</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45184</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45155</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>44586</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>44636</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45362</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44509</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>45204</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>46133</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
